--- a/output/2026-10-10_23_Serbia_Branicevski_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-10_23_Serbia_Branicevski_ATEX_Equipment-Services.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -521,8 +521,6 @@
           <t>Consulenza e certificazione per sicurezza sul lavoro, protezione antincendio e da esplosione (ATEX) - servizi B2B alle imprese</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Ente privato fondato nel 1990 (direttore Dejan Radujkov, fonte biznis.rs), sede confermata in Kraljevica Marka 11, 21101 Novi Sad (directory PlanPlus). Eroga servizi di consulenza/certificazione a pagamento verso imprese terze (B2B), non e' un ente pubblico puro. Un numero di telefono trovato in una fonte terza era in realta' associato ad un'altra azienda allo stesso indirizzo, quindi non riportato per evitare errori. Nessuna sede nel distretto Branicevski.</t>
@@ -555,8 +553,6 @@
           <t>Certificazione di conformita', ispezione e test di apparecchiature per atmosfere potenzialmente esplosive (servizi ATEX a pagamento per aziende terze)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Esistenza e attivita' confermate tramite documenti ufficiali pubblicati su vinca.rs (moduli 'Zahtev za OU CENEx' e 'Zahtev korisnika' per richiesta certificati di conformita' secondo il Pravilnik ATEX serbo, Sl. glasnik RS 10/17 e 21/20). Pur facendo parte di un istituto pubblico di ricerca, CENEx eroga servizi commerciali di certificazione/test a pagamento verso aziende terze (B2B), quindi non e' stato scartato come 'ente pubblico puro'. Non e' un distributore di prodotti ma un fornitore di servizi di conformita' ATEX. Nessuna sede nel distretto Branicevski.</t>
@@ -564,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -589,8 +585,6 @@
           <t>Aspiratori/otprasivaci industriali certificati ATEX Zona 22 (classi polvere M e H)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verificata la presenza della gamma prodotti ATEX Zona 22 (es. NT 75/1 Me Ec M/H Z22, IVC 60/30 Ap M Z22) sul sito ufficiale Karcher Serbia. Canale diretto del produttore, non distributore indipendente; nessun rivenditore locale specifico individuato nel distretto Branicevski tramite lo strumento dealer-search del sito.</t>
@@ -598,7 +592,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -623,8 +617,6 @@
           <t>Servizi di riparazione/revisione (overhaul) di apparecchiature Ex secondo norma SRPS EN IEC 60079-19 (motori elettrici fino a 160 kW/0,4kV, protezioni Exd/Exe/Exec) - servizio tecnico certificato</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Confermato certificato ufficiale (rilasciato da Institut za preventivu, Novi Sad) pubblicato su nis.rs per riparazione/revisione di apparecchiature Ex secondo SRPS EN IEC 60079-19, valido fino al 27/12/2026. La pagina istituzionale NIS dichiara che le proprie capacita' di servizio (incluse le controllate Naftagas Oilfield Services e Naftagas Tehnicki servisi) possono essere erogate anche a terzi oltre al fabbisogno interno del gruppo. Non e' stata trovata conferma specifica di contratti di riparazione Ex con clienti esterni al gruppo NIS: verificare direttamente la reale apertura commerciale a terzi B2B. Nessuna sede nel distretto Branicevski.</t>
